--- a/shared/words/E3_单词汇总.xlsx
+++ b/shared/words/E3_单词汇总.xlsx
@@ -1294,6 +1294,11 @@
           <t>words/einheit3/haben.mp3</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Um acht Uhr haben wir Deutschunterricht.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1316,6 +1321,11 @@
           <t>words/einheit3/laufen.mp3</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich laufe schnell.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1473,6 +1483,11 @@
           <t>words/einheit3/sehen.mp3</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich sehe dort einen Baum.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2346,6 +2361,11 @@
           <t>words/einheit3/immer.mp3</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er kommt immer zu spät.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2422,6 +2442,11 @@
           <t>words/einheit3/früh.mp3</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stehst du so früh auf?</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2444,6 +2469,11 @@
           <t>words/einheit3/wann.mp3</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wann hast du Zeit?</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2466,6 +2496,11 @@
           <t>words/einheit3/aktiv.mp3</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sie ist sehr aktiv.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2488,6 +2523,11 @@
           <t>words/einheit3/nicht.mp3</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Am Nachmittag lernen die Kinder nicht.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2510,6 +2550,11 @@
           <t>words/einheit3/nur.mp3</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Lehrerin spricht im Unterricht nur Deutsch.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2937,6 +2982,11 @@
           <t>words/einheit3/endlich.mp3</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Endlich sind die Ferien da.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2959,6 +3009,11 @@
           <t>words/einheit3/oft.mp3</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sie fährt oft Fahrrad.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2981,6 +3036,11 @@
           <t>words/einheit3/alt.mp3</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Der Hof ist alt.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3003,6 +3063,11 @@
           <t>words/einheit3/etwa.mp3</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das dauert etwa zehn Minuten.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3023,6 +3088,11 @@
       <c r="F66" t="inlineStr">
         <is>
           <t>words/einheit3/interessant.mp3</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist aber interessant.</t>
         </is>
       </c>
     </row>
